--- a/RequirementDocs/Pin Code corrections.xlsx
+++ b/RequirementDocs/Pin Code corrections.xlsx
@@ -10,11 +10,12 @@
     <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Corrections" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Evidence - source sheet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Evidence - India Post" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Coverage audit" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Unplaceable codes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Sheet edits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Evidence - sheet now" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Evidence - India Post" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Coverage audit" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Unplaceable codes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Verification" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,10 +472,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -485,7 +486,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>THE SOURCE FILE IS NEVER EDITED</t>
+          <t>THE SPREADSHEET IS THE ONLY SOURCE</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr"/>
@@ -498,163 +499,163 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>UNCHANGED. Not one cell has been written. It stays the source so a fresh vendor export can replace it wholesale without losing anything.</t>
+          <t>CORRECTED IN PLACE. 48 rows rewritten, 7 added. The importer reads this file and nothing else.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>So where do corrections live?</t>
+          <t>Are there overrides in the code?</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>In code: api/app/features/geo/pincode_overrides.py. The importer applies them on every upload and REPORTS each one, so a correction can never diverge from the file silently.</t>
+          <t>NO. There used to be. They were deleted, because an override outranks the file - so fixing the file stopped fixing the master, and you could not tell from the sheet what the master would end up holding.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>What happens if the vendor fixes the sheet?</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>The override becomes a no-op and is reported as 'agreed' instead of 'applied'. Nothing needs deleting.</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HOW TO CHANGE A PINCODE</t>
+        </is>
+      </c>
       <c r="B6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>HOW TO READ THIS WORKBOOK</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Add one</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Add a row: Region, State, District, Pin Code. One row per district if it spans several.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Corrections</t>
+          <t>Move it to another state</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Every change, one row each. Start here.</t>
+          <t>Change the state on ALL its rows. Majority of rows wins.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Evidence - source sheet</t>
+          <t>Change its district</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Every row of the vendor file behind those changes.</t>
+          <t>Change the district on its rows. Links are replaced, not merged.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Evidence - India Post</t>
+          <t>Then</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Every post office India Post lists for those pincodes.</t>
+          <t>Upload on Super Admin -&gt; Geography. You get a dry-run preview before anything is written.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Coverage audit</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>The reconciliation against India Post - what was checked, found, and is still open.</t>
-        </is>
-      </c>
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Unplaceable codes</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>The 96 still outstanding, and what they turned out to be.</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SAFETY RULES IN THE IMPORTER</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Additive</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>The checks run afterwards, and their results.</t>
+          <t>Creates and updates what the file names; never deletes what it omits. A one-state sheet is safe to upload alone.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Ties are refused</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>A pincode split evenly between two states is rejected BY NAME rather than guessed at.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>DATES</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>#N/A rows are dropped</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>A region or state of #N/A means the vendor's own lookup failed. Those rows are skipped and reported.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Round 1</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21 - state conflicts and stateless codes</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Round 2</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-22 - missing districts, the 96 identified, and a full coverage audit</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>REVERTING</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Authority</t>
+          <t>The original sheet</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>India Post: api.postalpincode.in, plus office-name lookups</t>
+          <t>git show a2d8f65:"RequirementDocs/Reliance Green Tech Pin Code.xlsx" &gt; original.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>The edit script</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>RequirementDocs/apply-pincode-corrections.py - declarative, re-runnable on a fresh vendor export</t>
         </is>
       </c>
     </row>
@@ -669,11 +670,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -697,396 +698,324 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rows in the vendor sheet</t>
+          <t>Rows in the sheet</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>165,627</t>
+          <t>165,634</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>one per post office, ~8.5 per pincode</t>
+          <t>was 165,627 - seven added</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Rows the vendor could not resolve</t>
+          <t>Rows rewritten</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>region '#N/A', state 'NA'</t>
+          <t>see 'Sheet edits'</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Rows added</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>six pincodes; 393155 needs two, it spans two districts</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ROUND 1 - state conflicts</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="inlineStr"/>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Pincodes listed under TWO states</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>all 52 checked against India Post</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>WHAT WAS FIXED</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; sheet was already right</t>
+          <t>Districts filled in (was NA)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>5 pincodes</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>no change made</t>
+          <t>222101, 390008, 605012, 804454, 494446</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; CORRECTED</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>District corrected (was wrong)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1 pincode</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Corrections #1-6</t>
+          <t>494446 - Raipur -&gt; Bijapur</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Pincodes with no state at all</t>
+          <t>States made consistent</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6 pincodes</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>present only on #N/A rows</t>
+          <t>border-straddling codes the file could not resolve</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; state RECOVERED</t>
+          <t>Pincodes added</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Corrections #7-10</t>
+          <t>India Post has them; the export never did</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; left out (Nodal Delivery Centres)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>see 'Unplaceable codes'</t>
-        </is>
-      </c>
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MASTER TODAY</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr"/>
       <c r="C12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ROUND 2 - the missing-data audit</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr"/>
+          <t>Regions / States / Districts</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>5 / 36 / 754</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>states complete: 28 states + 8 UTs</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Pincodes in the master with no district</t>
+          <t>Pincodes</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>4 -&gt; 0</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Corrections #11-14</t>
-        </is>
-      </c>
+          <t>19,496</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Pincodes India Post has, sheet does NOT</t>
+          <t>Pincodes with no district</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>6 ADDED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Corrections #15-20</t>
+          <t>was 4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Pincodes with a WRONG district</t>
+          <t>Pincodes in 2+ districts</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>1 CORRECTED</t>
+          <t>1,209</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Corrections #21</t>
+          <t>1,142 in two, 58 in three, 9 in four</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Sorting hubs found but not added</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>110050, same call as the 96</t>
-        </is>
-      </c>
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PROOF THE SHEET IS ENOUGH</t>
+        </is>
+      </c>
       <c r="B18" s="3" t="inlineStr"/>
       <c r="C18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>MASTER TODAY</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr"/>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Re-import, overrides deleted</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>pincodes c0 u19496 m0</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>nothing created, nothing moved</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Regions</t>
+          <t>District links changed</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0 created, 0 deleted</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Central holds no states</t>
+          <t>checked on the real write path</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>States</t>
+          <t>Overrides reported</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>28 states + 8 UTs - complete, none missing</t>
+          <t>there are none left to report</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Districts</t>
+          <t>Rows skipped</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>702</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>complete for every pincode we hold</t>
+          <t>was 715 - exactly the 13 #N/A rows filled in</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Pincodes</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>19,496</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>was 19,490 - six added</t>
-        </is>
-      </c>
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Pincodes with no district</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>was 4</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>STILL OPEN</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Pincodes in 2+ districts</t>
+          <t>Full India Post reconciliation</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>1,209</t>
+          <t>~95 may still be missing</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>1,142 in two, 58 in three, 9 in four</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
-      <c r="C26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>WHAT IS STILL OPEN</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr"/>
-      <c r="C27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Full reconciliation</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>see the 'Coverage audit' sheet - needs a free data.gov.in API key</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Estimated pincodes still missing</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>~100</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>0.5% of the sample was missing; 6 of them found and added</t>
+          <t>needs a free data.gov.in key - see 'Coverage audit'</t>
         </is>
       </c>
     </row>
@@ -1101,29 +1030,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="62" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="66" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Every change made to the geography master. 14 in total: 6 states corrected, 4 states recovered, 4 districts recovered. BEFORE/AFTER describe the MASTER, not the spreadsheet - the spreadsheet is never written to.</t>
+          <t>Every correction, one row each. All of them are now IN the spreadsheet - there is no code that overrides the file. 'Sheet now reads' is what the file actually contains today.</t>
         </is>
       </c>
     </row>
@@ -1145,57 +1069,32 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>Sheet said</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>What the vendor sheet says</t>
+          <t>Changed to</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Rows in sheet</t>
+          <t>Sheet now reads</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>Sheet's own verdict</t>
+          <t>What India Post says</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>What India Post says</t>
+          <t>Why</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>BEFORE (in the master)</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>AFTER (in the master)</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>Field changed</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>Why the sheet was not followed</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>Where the rule lives</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>How it was applied</t>
+          <t>How</t>
         </is>
       </c>
     </row>
@@ -1205,65 +1104,42 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>605014</t>
+          <t>222101</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>State corrected</t>
+          <t>District filled in</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NA / NA</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Tamil Nadu x2, Puducherry x2</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>4</v>
+          <t>UTTAR PRADESH / JAUNPUR</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>UTTAR PRADESH / JAUNPUR x1 ; UTTAR PRADESH / JAUNPUR x1 ; UTTAR PRADESH / JAUNPUR x1 ; UTTAR PRADESH / JAUNPUR x1 ; UTTAR PRADESH / JAUNPUR x1 ; UTTAR PRADESH / JAUNPUR x1</t>
+        </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>TIE</t>
+          <t>8 offices - Jaunpur</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Pondicherry x2, Tamil Nadu x2</t>
+          <t>Vendor lookup failed on every row (#N/A / NA / NA). India Post: 8 offices, all Jaunpur.</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>(importer would have REJECTED it)</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Puducherry</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>Sheet tied 2-2 and India Post is also tied 2-2. Broken by the sub post office, Pondicherry University, which the branch offices hang off.</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.STATE_OVERRIDES</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1273,65 +1149,42 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>605106</t>
+          <t>390008</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>State corrected</t>
+          <t>District filled in</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NA / NA</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Tamil Nadu x5, Puducherry x5</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>10</v>
+          <t>GUJARAT / VADODARA</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>GUJARAT / VADODARA x1</t>
+        </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>TIE</t>
+          <t>1 offices - Vadodara</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Tamil Nadu x5, Pondicherry x5</t>
+          <t>Vendor lookup failed on its only row. India Post: Vadodara.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>(importer would have REJECTED it)</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Puducherry</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Sheet tied 5-5 and India Post is also tied 5-5. Broken by the sub post office, Nettapakkam.</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>pincode_overrides.STATE_OVERRIDES</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Applied at import</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1341,65 +1194,42 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>605107</t>
+          <t>494446</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>State corrected</t>
+          <t>District CORRECTED</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>CHHATTISGARH / RAIPUR ; NA / NA</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Puducherry x4, Tamil Nadu x4</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>8</v>
+          <t>CHHATTISGARH / BIJAPUR ; CHHATTISGARH / BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1 ; CHHATTISGARH / BIJAPUR x1</t>
+        </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>TIE</t>
+          <t>9 offices - Bijapur(CGH)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Tamil Nadu x5, Pondicherry x3</t>
+          <t>Sheet said RAIPUR on all 18 rows. All 9 India Post offices are in Bijapur, ~300km away.</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>(importer would have REJECTED it)</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Tamil Nadu</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>Sheet tied 4-4 with Puducherry. India Post breaks it 5-3 for Tamil Nadu.</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.STATE_OVERRIDES</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1409,65 +1239,42 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>607403</t>
+          <t>605012</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>State corrected</t>
+          <t>District filled in</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NA / NA</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Puducherry x2, Tamil Nadu x1</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>3</v>
+          <t>PUDUCHERRY / PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY / PONDICHERRY x1</t>
+        </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>1 offices - Pondicherry</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Tamil Nadu x2, Pondicherry x1</t>
+          <t>Vendor lookup failed on its only row. India Post: Pondicherry.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Puducherry</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Tamil Nadu</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Sheet says Puducherry 2-1. India Post has 2 offices in Tamil Nadu (Villupuram, Cuddalore) against 1 in Puducherry.</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>pincode_overrides.STATE_OVERRIDES</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>Applied at import</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1477,65 +1284,42 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>781029</t>
+          <t>605014</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>State corrected</t>
+          <t>State made consistent</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>TAMIL NADU / VILLUPURAM</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Meghalaya x1, Assam x1</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>2</v>
+          <t>PUDUCHERRY / PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1</t>
+        </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>TIE</t>
+          <t>4 offices - Pondicherry, Villupuram</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Assam x2</t>
+          <t>Sheet tied 2-2 with Tamil Nadu; India Post also tied. Broken by the Sub Post Office, Pondicherry University.</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>(importer would have REJECTED it)</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Assam</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>Sheet tied 1-1 with Meghalaya. Both India Post offices are in Kamrup, Assam.</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.STATE_OVERRIDES</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1545,65 +1329,42 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>781131</t>
+          <t>605106</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>State corrected</t>
+          <t>State made consistent</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>TAMIL NADU / VILLUPURAM ; TAMIL NADU / CUDDALORE</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya x3, Assam x1</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>4</v>
+          <t>PUDUCHERRY / PONDICHERRY ; PUDUCHERRY / PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1 ; PUDUCHERRY / PONDICHERRY x1</t>
+        </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>10 offices - Cuddalore, Pondicherry, Villupuram</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Assam x4</t>
+          <t>Sheet tied 5-5 with Tamil Nadu; India Post also tied. Broken by the Sub Post Office, Nettapakkam.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Assam</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Sheet says Meghalaya 3-1. All four post offices are in Kamrup, Assam. 781xxx is the Guwahati circle; Meghalaya is 793xxx/794xxx.</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>pincode_overrides.STATE_OVERRIDES</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>Applied at import</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1613,65 +1374,42 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>222101</t>
+          <t>605107</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>State recovered</t>
+          <t>State made consistent</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>PUDUCHERRY / PONDICHERRY</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>#N/A / NA / NA on every row</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>6</v>
+          <t>TAMIL NADU / VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>TAMIL NADU / VILLUPURAM x1 ; TAMIL NADU / VILLUPURAM x1 ; TAMIL NADU / VILLUPURAM x1 ; TAMIL NADU / VILLUPURAM x1 ; TAMIL NADU / VILLUPURAM x1 ; TAMIL NADU / VILLUPURAM x1 ; TAMIL NADU / VILLUPURAM x1 ; TAMIL NADU / VILLUPURAM x1</t>
+        </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>none - no state at all</t>
+          <t>8 offices - Pondicherry, Villupuram</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Sheet tied 4-4 with Puducherry. India Post breaks it 5-3 for Tamil Nadu.</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>(would not have been imported)</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Only on #N/A rows; India Post: Uttar Pradesh.</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.RECOVERED</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1681,65 +1419,42 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>390008</t>
+          <t>607403</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>State recovered</t>
+          <t>State made consistent</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>PUDUCHERRY / PONDICHERRY</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>#N/A / NA / NA on every row</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
+          <t>TAMIL NADU / CUDDALORE</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>TAMIL NADU / CUDDALORE x1 ; TAMIL NADU / CUDDALORE x1 ; TAMIL NADU / CUDDALORE x1</t>
+        </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>none - no state at all</t>
+          <t>3 offices - Cuddalore, Pondicherry, Villupuram</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Sheet said Puducherry 2-1. India Post has 2 of 3 offices in Tamil Nadu.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>(would not have been imported)</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Gujarat</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Only on #N/A rows; India Post: Gujarat.</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>pincode_overrides.RECOVERED</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>Applied at import</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1749,65 +1464,42 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>605012</t>
+          <t>781029</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>State recovered</t>
+          <t>State made consistent</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>MEGHALAYA / RI BHOI</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>#N/A / NA / NA on every row</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>1</v>
+          <t>ASSAM / KAMRUP METRO</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>ASSAM / KAMRUP METRO x1 ; ASSAM / KAMRUP METRO x1</t>
+        </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>none - no state at all</t>
+          <t>2 offices - Kamrup</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Sheet tied 1-1 with Meghalaya. Both India Post offices are in Kamrup, Assam.</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>(would not have been imported)</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Puducherry</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Only on #N/A rows; India Post: Puducherry.</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.RECOVERED</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1817,65 +1509,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>804454</t>
+          <t>781131</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>State recovered</t>
+          <t>State made consistent</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>MEGHALAYA / RI BHOI</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>#N/A / NA / NA on every row</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>2</v>
+          <t>ASSAM / KAMRUP</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>ASSAM / KAMRUP x1 ; ASSAM / KAMRUP x1 ; ASSAM / KAMRUP x1 ; ASSAM / KAMRUP x1</t>
+        </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>none - no state at all</t>
+          <t>4 offices - Kamrup</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Sheet said Meghalaya 3-1. All 4 India Post offices are in Kamrup, Assam.</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>(would not have been imported)</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Bihar</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Only on #N/A rows; India Post: Bihar.</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>pincode_overrides.RECOVERED</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>Applied at import</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1885,65 +1554,42 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>222101</t>
+          <t>804454</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>District recovered</t>
+          <t>District filled in</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>NA / NA</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>district column is NA on every row</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>6</v>
+          <t>BIHAR / PATNA</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>BIHAR / PATNA x1 ; BIHAR / PATNA x1</t>
+        </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>none - no district</t>
+          <t>10 offices - Patna</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Jaunpur</t>
+          <t>Vendor lookup failed on both rows. India Post: Patna.</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Uttar Pradesh, no district</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Jaunpur</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>District was NA on every row; India Post: Jaunpur.</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.DISTRICT_RECOVERED</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
+          <t>row edit in the sheet</t>
         </is>
       </c>
     </row>
@@ -1953,65 +1599,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>390008</t>
+          <t>335705</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>District recovered</t>
+          <t>Pincode ADDED</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>(no row at all)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>district column is NA on every row</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1</v>
+          <t>RAJASTHAN / GANGANAGAR</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>RAJASTHAN / GANGANAGAR x1</t>
+        </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>none - no district</t>
+          <t>2 offices, all Delivery - Ganganagar</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Absent from the export entirely; India Post has it as a live delivery pincode.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Gujarat, no district</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Vadodara</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>District was NA on every row; India Post: Vadodara.</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>pincode_overrides.DISTRICT_RECOVERED</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
+          <t>row added to the sheet</t>
         </is>
       </c>
     </row>
@@ -2021,65 +1644,42 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>605012</t>
+          <t>364485</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>District recovered</t>
+          <t>Pincode ADDED</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>(no row at all)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>district column is NA on every row</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>1</v>
+          <t>GUJARAT / RAJKOT</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>GUJARAT / RAJKOT x1</t>
+        </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>none - no district</t>
+          <t>5 offices, all Delivery - Rajkot</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Absent from the export entirely; India Post has it as a live delivery pincode.</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Puducherry, no district</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Pondicherry</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>District was NA on every row; India Post: Pondicherry.</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.DISTRICT_RECOVERED</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
+          <t>row added to the sheet</t>
         </is>
       </c>
     </row>
@@ -2089,65 +1689,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>804454</t>
+          <t>393155</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>District recovered</t>
+          <t>Pincode ADDED</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>(no row at all)</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>district column is NA on every row</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>2</v>
+          <t>GUJARAT / NARMADA</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>GUJARAT / NARMADA x1 ; GUJARAT / BHARUCH x1</t>
+        </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>none - no district</t>
+          <t>6 offices, all Delivery - Bharuch, Narmada</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Absent from the export entirely; India Post has it as a live delivery pincode.</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Bihar, no district</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Patna</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>District was NA on every row; India Post: Patna.</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>pincode_overrides.DISTRICT_RECOVERED</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
+          <t>row added to the sheet</t>
         </is>
       </c>
     </row>
@@ -2157,7 +1734,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>335705</t>
+          <t>396424</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -2165,53 +1742,34 @@
           <t>Pincode ADDED</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>(no row at all)</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>not in the sheet at all - no row</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0</v>
+          <t>GUJARAT / NAVSARI</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>GUJARAT / NAVSARI x1</t>
+        </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>1 offices, all Delivery - Navsari</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>2 offices, all Delivery - Ganganagar</t>
+          <t>Absent from the export entirely; India Post has it as a live delivery pincode.</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>(absent from the master)</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Rajasthan / Ganganagar</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>pincode + district</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>Absent from the sheet entirely. India Post: 3 F D M B.O and Sardargarh S.O, both Delivery, Ganganagar.</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.MISSING_PINCODES</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
+          <t>row added to the sheet</t>
         </is>
       </c>
     </row>
@@ -2221,7 +1779,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>364485</t>
+          <t>396440</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2229,53 +1787,34 @@
           <t>Pincode ADDED</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>(no row at all)</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>not in the sheet at all - no row</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0</v>
+          <t>GUJARAT / NAVSARI</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>GUJARAT / NAVSARI x1</t>
+        </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2 offices, all Delivery - Navsari</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>5 offices, all Delivery - Rajkot</t>
+          <t>Absent from the export entirely; India Post has it as a live delivery pincode.</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>(absent from the master)</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>Gujarat / Rajkot</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>pincode + district</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>Absent from the sheet entirely. India Post: 5 offices, all Delivery — Amarnagar S.O, Devla, Khirasara and others in Rajkot.</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>pincode_overrides.MISSING_PINCODES</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
+          <t>row added to the sheet</t>
         </is>
       </c>
     </row>
@@ -2285,7 +1824,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>393155</t>
+          <t>845102</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2293,315 +1832,40 @@
           <t>Pincode ADDED</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>(no row at all)</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>not in the sheet at all - no row</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0</v>
+          <t>BIHAR / PASHCHIM CHAMPARAN</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>BIHAR / PASHCHIM CHAMPARAN x1</t>
+        </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>1 offices, all Delivery - West Champaran</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>6 offices, all Delivery - Bharuch, Narmada</t>
+          <t>Absent from the export entirely; India Post has it as a live delivery pincode.</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>(absent from the master)</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>Gujarat / Narmada, Bharuch</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>pincode + district</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>Absent from the sheet entirely. India Post: 6 offices, all Delivery — Bhilvashi, Gora and Indravarna in Narmada, Gora Colony in Bharuch.</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.MISSING_PINCODES</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>396424</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Pincode ADDED</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>not in the sheet at all - no row</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>1 offices, all Delivery - Navsari</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>(absent from the master)</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>Gujarat / Navsari</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>pincode + district</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>Absent from the sheet entirely. India Post: Kabilpore S.O, Delivery, Navsari.</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>pincode_overrides.MISSING_PINCODES</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>396440</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Pincode ADDED</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>not in the sheet at all - no row</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>2 offices, all Delivery - Navsari</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>(absent from the master)</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>Gujarat / Navsari</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>pincode + district</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>Absent from the sheet entirely. India Post: Karadi S.O and Machhad B.O, both Delivery, Navsari.</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.MISSING_PINCODES</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>845102</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Pincode ADDED</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>not in the sheet at all - no row</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>1 offices, all Delivery - West Champaran</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>(absent from the master)</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>Bihar / Pashchim Champaran</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>pincode + district</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>Absent from the sheet entirely. India Post: Gaunaha S.O, Delivery, West Champaran — the master spells it Pashchim Champaran.</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>pincode_overrides.MISSING_PINCODES</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>District CORRECTED</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Raipur on all 18 rows</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Raipur</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>9 offices, all Bijapur(CGH)</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Chhattisgarh / Raipur</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>Chhattisgarh / Bijapur</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>district (replaced)</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>Sheet says Raipur on all 18 rows. All 9 India Post offices (Bhopalpatnam S.O and its branches) are in Bijapur, ~300km away.</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>pincode_overrides.DISTRICT_OVERRIDES</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>Applied at import + app.scripts.link_recovered_districts --apply</t>
+          <t>row added to the sheet</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2613,20 +1877,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Every single row of 'Reliance Green Tech Pin Code.xlsx' that names one of the 10 corrected pincodes, exactly as the file has it. This is what the importer read. Read-only - nothing here was written back.</t>
+          <t>The literal spreadsheet edits, exactly as apply-pincode-corrections.py makes them. 48 rows rewritten across 11 pincodes, 7 rows added.</t>
         </is>
       </c>
     </row>
@@ -2638,172 +1902,184 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Row # in the vendor file</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>Was</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>Why</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>605014</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>88296</v>
+          <t>222101</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>#N/A / NA / NA</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TAMIL NADU</t>
+          <t>North / UTTAR PRADESH / JAUNPUR</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>VILLUPURAM</t>
+          <t>District filled in</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>605014</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>131093</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>PUDUCHERRY</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>PONDICHERRY</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>390008</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>#N/A / NA / NA</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>West / GUJARAT / VADODARA</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>District filled in</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>605014</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>152707</v>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West / CHHATTISGARH / RAIPUR</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>West / CHHATTISGARH / BIJAPUR</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>PONDICHERRY</t>
+          <t>District CORRECTED</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>605014</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>152708</v>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>#N/A / NA / NA</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TAMIL NADU</t>
+          <t>West / CHHATTISGARH / BIJAPUR</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>VILLUPURAM</t>
+          <t>District CORRECTED</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>605106</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>21975</v>
+          <t>605012</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>#N/A / NA / NA</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>TAMIL NADU</t>
+          <t>South / PUDUCHERRY / PONDICHERRY</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>VILLUPURAM</t>
+          <t>District filled in</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>605106</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>30695</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>PUDUCHERRY</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>PONDICHERRY</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>605014</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>South / TAMIL NADU / VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>South / PUDUCHERRY / PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>State made consistent</t>
         </is>
       </c>
     </row>
@@ -2813,22 +2089,24 @@
           <t>605106</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>50314</v>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>South / TAMIL NADU / VILLUPURAM</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>TAMIL NADU</t>
+          <t>South / PUDUCHERRY / PONDICHERRY</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>CUDDALORE</t>
+          <t>State made consistent</t>
         </is>
       </c>
     </row>
@@ -2838,827 +2116,348 @@
           <t>605106</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>50315</v>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>South / TAMIL NADU / CUDDALORE</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>South / PUDUCHERRY / PONDICHERRY</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>PONDICHERRY</t>
+          <t>State made consistent</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>605106</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>88294</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>PUDUCHERRY</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>PONDICHERRY</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>605107</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>South / PUDUCHERRY / PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>South / TAMIL NADU / VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>State made consistent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>605106</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>88295</v>
+          <t>607403</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>South / PUDUCHERRY / PONDICHERRY</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>TAMIL NADU</t>
+          <t>South / TAMIL NADU / CUDDALORE</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>VILLUPURAM</t>
+          <t>State made consistent</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>605106</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>118967</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>PUDUCHERRY</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>PONDICHERRY</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>781029</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>East / MEGHALAYA / RI BHOI</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>East / ASSAM / KAMRUP METRO</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>State made consistent</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>605106</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>118968</v>
+          <t>781131</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East / MEGHALAYA / RI BHOI</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>East / ASSAM / KAMRUP</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>PONDICHERRY</t>
+          <t>State made consistent</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>605106</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>118969</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>TAMIL NADU</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>VILLUPURAM</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>804454</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>rewritten</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>#N/A / NA / NA</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>East / BIHAR / PATNA</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>District filled in</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>605106</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>152706</v>
+          <t>335705</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>(no row)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>TAMIL NADU</t>
+          <t>West / RAJASTHAN / GANGANAGAR</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>CUDDALORE</t>
+          <t>Pincode ADDED</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>605107</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>22032</v>
+          <t>364485</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>(no row)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>West / GUJARAT / RAJKOT</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>PONDICHERRY</t>
+          <t>Pincode ADDED</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>605107</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>50375</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>PUDUCHERRY</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>PONDICHERRY</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>393155</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>(no row)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>West / GUJARAT / NARMADA</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Pincode ADDED</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>605107</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>50376</v>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>TAMIL NADU</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>VILLUPURAM</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>393155</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>(no row)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>West / GUJARAT / BHARUCH</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Pincode ADDED</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>605107</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>61048</v>
+          <t>396424</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>(no row)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TAMIL NADU</t>
+          <t>West / GUJARAT / NAVSARI</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>VILLUPURAM</t>
+          <t>Pincode ADDED</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>605107</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>88340</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>PUDUCHERRY</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>PONDICHERRY</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>396440</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>(no row)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>West / GUJARAT / NAVSARI</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Pincode ADDED</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>605107</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>88341</v>
+          <t>845102</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>(no row)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TAMIL NADU</t>
+          <t>East / BIHAR / PASHCHIM CHAMPARAN</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>VILLUPURAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>605107</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>119015</v>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>TAMIL NADU</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>VILLUPURAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>605107</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>119016</v>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>PUDUCHERRY</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>PONDICHERRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>607403</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>21986</v>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>TAMIL NADU</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>CUDDALORE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>607403</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>118974</v>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>PUDUCHERRY</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>PONDICHERRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>607403</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>131096</v>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>PUDUCHERRY</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>PONDICHERRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>781029</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>35109</v>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>MEGHALAYA</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>RI BHOI</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>781029</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>95313</v>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>ASSAM</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>KAMRUP METRO</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>781131</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>4962</v>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>MEGHALAYA</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>RI BHOI</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>781131</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>71366</v>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>MEGHALAYA</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>RI BHOI</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>781131</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>103127</v>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>MEGHALAYA</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>RI BHOI</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>781131</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>128106</v>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>ASSAM</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>KAMRUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>222101</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>27193</v>
-      </c>
-      <c r="C34" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>222101</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>27194</v>
-      </c>
-      <c r="C35" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>222101</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>27196</v>
-      </c>
-      <c r="C36" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>222101</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>125890</v>
-      </c>
-      <c r="C37" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>222101</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>131657</v>
-      </c>
-      <c r="C38" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>222101</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>156525</v>
-      </c>
-      <c r="C39" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>390008</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>128740</v>
-      </c>
-      <c r="C40" s="3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>605012</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>61039</v>
-      </c>
-      <c r="C41" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>804454</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>133741</v>
-      </c>
-      <c r="C42" s="3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>804454</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>133742</v>
-      </c>
-      <c r="C43" s="3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pincode ADDED</t>
         </is>
       </c>
     </row>
@@ -3671,6 +2470,2002 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>What the corrected spreadsheet contains today for every pincode that was touched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Pincode</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Row #</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Identical rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>222101</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>27193</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>UTTAR PRADESH</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>JAUNPUR</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>222101</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>27194</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>UTTAR PRADESH</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>JAUNPUR</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>222101</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>27196</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>UTTAR PRADESH</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>JAUNPUR</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>222101</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>125890</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>UTTAR PRADESH</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>JAUNPUR</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>222101</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>131657</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>UTTAR PRADESH</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>JAUNPUR</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>222101</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>156525</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>UTTAR PRADESH</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>JAUNPUR</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>335705</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>165629</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>RAJASTHAN</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>GANGANAGAR</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>364485</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>165630</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>GUJARAT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>RAJKOT</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>390008</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>128740</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>GUJARAT</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>VADODARA</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>393155</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>165631</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>GUJARAT</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>NARMADA</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>393155</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>165632</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>GUJARAT</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BHARUCH</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>396424</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>165633</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>GUJARAT</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>NAVSARI</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>396440</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>165634</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>GUJARAT</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>NAVSARI</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2270</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>2271</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2272</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2273</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>29375</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>34200</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>34201</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>34202</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>34203</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>34204</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>66720</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>66721</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>66722</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>66723</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>100954</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>100955</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>100956</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>100957</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>133945</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>133946</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>133947</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>CHHATTISGARH</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>BIJAPUR</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>605012</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>61039</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>605014</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>88296</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>605014</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>131093</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>605014</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>152707</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>605014</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>152708</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>605106</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>21975</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>605106</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>30695</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>605106</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>50314</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>605106</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>50315</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>605106</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>88294</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>605106</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>88295</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>605106</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>118967</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>605106</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>118968</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>605106</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>118969</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>605106</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>152706</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>PUDUCHERRY</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>PONDICHERRY</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>605107</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>22032</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>605107</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>50375</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>605107</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>50376</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>605107</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>61048</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>605107</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>88340</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>605107</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>88341</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>605107</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>119015</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>605107</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>119016</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>VILLUPURAM</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>607403</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>21986</v>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>CUDDALORE</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>607403</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>118974</v>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>CUDDALORE</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>607403</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>131096</v>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>TAMIL NADU</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>CUDDALORE</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>781029</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>35109</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>ASSAM</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>KAMRUP METRO</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>781029</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>95313</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>ASSAM</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>KAMRUP METRO</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>781131</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>4962</v>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>ASSAM</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>KAMRUP</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>781131</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>71366</v>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>ASSAM</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>KAMRUP</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>781131</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>103127</v>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>ASSAM</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>KAMRUP</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>781131</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>128106</v>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>ASSAM</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>KAMRUP</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>804454</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>133741</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>BIHAR</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>PATNA</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>804454</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>133742</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>BIHAR</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>PATNA</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>845102</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>165635</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>BIHAR</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>PASHCHIM CHAMPARAN</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3688,10 +4483,10 @@
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Every post office India Post lists for those same 10 pincodes, from api.postalpincode.in. Where the vendor sheet and this disagree, this wins. Ties were broken by the Sub Post Office, which is the administrative centre the Branch Post Offices hang off.</t>
+          <t>Every post office India Post lists for those pincodes. Where the vendor sheet and this disagreed, this won. Ties were broken by the Sub Post Office, the administrative centre the Branch Post Offices hang off.</t>
         </is>
       </c>
     </row>
@@ -6589,13 +7384,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6603,10 +7398,10 @@
     <col width="76" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>What was checked against India Post, what it found, and what is still open. The headline: nothing was lost from the vendor sheet, our states are complete, and where our districts disagree with India Post it is almost always because OUR data is newer. Six genuinely missing pincodes were found and added.</t>
+          <t>What was checked against India Post. Headline: nothing lost from the sheet, states complete, and where our districts disagree with India Post it is almost always because OUR data is newer. Six genuinely missing pincodes were found and added.</t>
         </is>
       </c>
     </row>
@@ -6630,7 +7425,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. Does the master hold everything the VENDOR SHEET contains?</t>
+          <t>1. Does the master hold everything the sheet contains?</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
@@ -6639,51 +7434,39 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>States</t>
+          <t>States / Districts / Pincodes</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>36/36, 754/754, all</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>PASS - nothing lost on import</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2. Are our states the real 36?</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>36 / 36</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>PASS - none lost</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Districts</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>754 / 754</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>PASS - none lost</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Pincodes</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>19,486 / 19,486</t>
-        </is>
-      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>PASS - none lost</t>
+          <t>PASS - 28 states + 8 UTs, none missing</t>
         </is>
       </c>
     </row>
@@ -6695,7 +7478,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2. Are our STATES the real 36?</t>
+          <t>3. Is our data right, per India Post?  (600-pincode sample, seed 20260822)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr"/>
@@ -6704,233 +7487,245 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Checked against 28 states + 8 union territories</t>
+          <t>State matches</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>36 / 36</t>
+          <t>571 / 579</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>PASS - none missing, none spurious</t>
+          <t>the 8 'mismatches' are spelling, or India Post being pre-2019 on Ladakh</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Real state errors</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="C10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>3. Is our data right, per India Post?  (600-pincode random sample, seed 20260822)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>District disagreements</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>167 / 579</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>nearly all are OUR DATA BEING NEWER</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Sampled</t>
+          <t>Real district errors</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>600 of 19,490</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>494446 - corrected</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Lookup errors</t>
+          <t>Not found by India Post</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
+          <t>21 / 600</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>NDC / sorting-hub category, same as the 96</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>State matches India Post</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>571 / 579</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>the 8 'mismatches' are all spelling ('chattisgarh') or India Post being PRE-2019 on Ladakh</t>
-        </is>
-      </c>
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Real state errors found</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>WHY SO MANY DISAGREEMENTS? India Post's directory is STALE</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
       <c r="C15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>District disagreements</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>505214</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>167 / 579</t>
+          <t>we say Peddapalli</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>nearly all are OUR DATA BEING NEWER - see below</t>
+          <t>India Post still says Karimnagar - Telangana split it in 2016</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Real district errors found</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>518411</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>we say Nandyal</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>494446 - Raipur should be Bijapur. CORRECTED.</t>
+          <t>India Post still says Kurnool - Andhra split it in 2022</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Not found by India Post</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>211003</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>21 / 600</t>
+          <t>we say Prayagraj</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>same NDC/sorting-hub category as the 96</t>
+          <t>India Post still says Allahabad - renamed 2018</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr"/>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>our data is NEWER</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>a disagreement is not automatically an error</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>WHY SO MANY DISTRICT DISAGREEMENTS?</t>
-        </is>
-      </c>
+      <c r="A20" s="3" t="inlineStr"/>
       <c r="B20" s="3" t="inlineStr"/>
       <c r="C20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>India Post's published directory is STALE</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>4. Does India Post have pincodes we don't?</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr"/>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>it still uses pre-2016 Telangana and pre-2022 Andhra districts</t>
-        </is>
-      </c>
+      <c r="C21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Example: Peddapalli</t>
+          <t>Directory size</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>we say Peddapalli</t>
+          <t>155,570 post offices</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>India Post still says Karimnagar (split in 2016)</t>
+          <t>data.gov.in resource 6176ee09-3d56-4a3b-8115-21841576b2f6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Example: Nandyal</t>
+          <t>Sample pulled</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>we say Nandyal</t>
+          <t>1,321 distinct pincodes</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>India Post still says Kurnool (split in 2022)</t>
+          <t>6.8% - the shared demo key returns 10 per call</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Example: Prayagraj</t>
+          <t>Missing found</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>we say Prayagraj</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>India Post still says Allahabad (renamed 2018)</t>
+          <t>6 added; 110050 is a sorting hub, left out</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Conclusion</t>
+          <t>Implied national gap</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>our data is NEWER</t>
+          <t>~100</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>a disagreement is not automatically an error</t>
+          <t>0.53% of the sample was missing</t>
         </is>
       </c>
     </row>
@@ -6942,7 +7737,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>4. Does India Post have pincodes we DON'T?  (data.gov.in directory)</t>
+          <t>STILL OPEN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr"/>
@@ -6951,133 +7746,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Directory size</t>
+          <t>Complete reconciliation</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>155,570 post offices</t>
+          <t>~95 still to find</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>resource 6176ee09-3d56-4a3b-8115-21841576b2f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Records we managed to pull</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>3,540</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>shared demo key returns 10 per call and rate-limits hard</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Distinct pincodes covered</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>1,321</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>6.8% of India's ~19,300</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Missing from our master</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>7 found</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>6 real and ADDED; 1 (110050) is a sorting hub, left out</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Implied national gap</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>~100 pincodes</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>0.53% of the sample was missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
-      <c r="B33" s="3" t="inlineStr"/>
-      <c r="C33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>STILL OPEN</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr"/>
-      <c r="C34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>A COMPLETE reconciliation</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>not possible with the shared key</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>register a free key at data.gov.in and re-run the sweep over all 155,570 records</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Estimated codes still to find</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>~95</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>all likely small rural B.O/S.O offices like the six added</t>
+          <t>register a free data.gov.in key and sweep all 155,570 records</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7108,10 +7787,10 @@
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>96 codes the vendor sheet carries ONLY on #N/A rows. ROUND 1 RECORDED THESE AS 'not pincodes at all'. THAT WAS WRONG. They are real post office codes. Every one looked up by name is a Nodal Delivery Centre, which India Post records with District: NA and State: NA because a hub is not a delivery area - which is exactly why the vendor's lookup wrote #N/A. They are left out because nobody lives at a distribution hub, so they are not service coverage. They can be added with a state (never a district) if you want them.</t>
+          <t>96 codes the sheet carries ONLY on #N/A rows. ROUND 1 RECORDED THESE AS 'not pincodes at all'. THAT WAS WRONG - they are real post office codes. Every one looked up by name is a Nodal Delivery Centre, which India Post records with District: NA and State: NA because a hub is not a delivery area - exactly why the vendor's lookup wrote #N/A. Left out because nobody lives at a distribution hub, so they are deliberately NOT corrected in the sheet.</t>
         </is>
       </c>
     </row>
@@ -11005,18 +11684,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11039,7 +11718,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Source sheet untouched</t>
+          <t>Sheet reproduces the master alone</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -11049,150 +11728,150 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>git reports no change to Reliance Green Tech Pin Code.xlsx</t>
+          <t>re-import with overrides deleted: pincodes c0 u19496 m0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Pincodes with no district</t>
+          <t>District links change on re-import</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0 created, 0 deleted</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GET /geo/pincodes?noDistrict=true -&gt; totalRecords 0 (was 4)</t>
+          <t>checked on the real write path, commit intercepted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Total pincodes</t>
+          <t>Overrides in the code</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>19,490</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>pincode_overrides.py and link_recovered_districts.py deleted</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Total districts</t>
+          <t>Rows skipped</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>702</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>unchanged - nothing new was created</t>
+          <t>was 715 - exactly the 13 #N/A rows filled in</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Total states</t>
+          <t>Rows rejected</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>matched against the official 28 states + 8 UTs; none missing</t>
+          <t>the NDC hubs, unchanged and correct</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Jaunpur, Uttar Pradesh</t>
+          <t>Pincodes with no district</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>46 pincodes</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>was 45, +1 from 222101</t>
+          <t>was 4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Vadodara, Gujarat</t>
+          <t>Total pincodes</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>62 pincodes</t>
+          <t>19,496</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>was 61, +1 from 390008</t>
+          <t>19,486 from the sheet + 4 filled + 6 added</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Pondicherry, Puducherry</t>
+          <t>Total districts</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>18 pincodes</t>
+          <t>754</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>was 17, +1 from 605012</t>
+          <t>no district orphaned; Ri Bhoi keeps 6 other pincodes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Patna, Bihar</t>
+          <t>Total states</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>71 pincodes</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>was 70, +1 from 804454</t>
+          <t>28 states + 8 UTs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Link script is idempotent</t>
+          <t>Tenant isolation</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -11202,14 +11881,14 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>second --apply run: 0 linked, 4 already correct</t>
+          <t>python -m app.scripts.audit_tenancy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Importer reports all 14</t>
+          <t>API compiles</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -11219,58 +11898,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>dry run lists 14 overrides incl. the 4 district ones</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Dry run hides nothing</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>district recoveries compute outside the dry-run guard</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Tenant isolation</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>python -m app.scripts.audit_tenancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>96 re-checked</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>96/96 not found</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>api.postalpincode.in, 2026-08-22</t>
+          <t>python -m compileall app</t>
         </is>
       </c>
     </row>
